--- a/registration_forms/025_facility_energy_benchmarking_registration--registration_forms.xlsx
+++ b/registration_forms/025_facility_energy_benchmarking_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'facility'}</t>
+          <t>facility</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Facility'}</t>
+          <t>Facility</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'utility_company'}</t>
+          <t>utility_company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Utility Company'}</t>
+          <t>Utility Company</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_2020,_'value':_2020}</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 2020, 'value': 2020}</t>
+          <t>2020</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2019,_'value':_2019}</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2019, 'value': 2019}</t>
+          <t>2019</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_2018,_'value':_2018}</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 2018, 'value': 2018}</t>
+          <t>2018</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_2017,_'value':_2017}</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 2017, 'value': 2017}</t>
+          <t>2017</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_2016,_'value':_2016}</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 2016, 'value': 2016}</t>
+          <t>2016</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_2015,_'value':_2015}</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 2015, 'value': 2015}</t>
+          <t>2015</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'alabama'}</t>
+          <t>alabama</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Alabama'}</t>
+          <t>Alabama</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'alaska',_'value':_'alaska'}</t>
+          <t>alaska</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Alaska', 'value': 'Alaska'}</t>
+          <t>Alaska</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'arizona',_'value':_'arizona'}</t>
+          <t>arizona</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Arizona', 'value': 'Arizona'}</t>
+          <t>Arizona</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'arkansas',_'value':_'arkansas'}</t>
+          <t>arkansas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Arkansas', 'value': 'Arkansas'}</t>
+          <t>Arkansas</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'california',_'value':_'california'}</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'California', 'value': 'California'}</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'colorado',_'value':_'colorado'}</t>
+          <t>colorado</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Colorado', 'value': 'Colorado'}</t>
+          <t>Colorado</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'connecticut',_'value':_'connecticut'}</t>
+          <t>connecticut</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Connecticut', 'value': 'Connecticut'}</t>
+          <t>Connecticut</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'delaware',_'value':_'delaware'}</t>
+          <t>delaware</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Delaware', 'value': 'Delaware'}</t>
+          <t>Delaware</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'florida',_'value':_'florida'}</t>
+          <t>florida</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Florida', 'value': 'Florida'}</t>
+          <t>Florida</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'georgia',_'value':_'georgia'}</t>
+          <t>georgia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Georgia', 'value': 'Georgia'}</t>
+          <t>Georgia</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'hawaii',_'value':_'hawaii'}</t>
+          <t>hawaii</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Hawaii', 'value': 'Hawaii'}</t>
+          <t>Hawaii</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'idaho',_'value':_'idaho'}</t>
+          <t>idaho</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Idaho', 'value': 'Idaho'}</t>
+          <t>Idaho</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'illinois',_'value':_'illinois'}</t>
+          <t>illinois</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Illinois', 'value': 'Illinois'}</t>
+          <t>Illinois</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'indiana',_'value':_'indiana'}</t>
+          <t>indiana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Indiana', 'value': 'Indiana'}</t>
+          <t>Indiana</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'iowa',_'value':_'iowa'}</t>
+          <t>iowa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Iowa', 'value': 'Iowa'}</t>
+          <t>Iowa</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'kansas',_'value':_'kansas'}</t>
+          <t>kansas</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 'Kansas', 'value': 'Kansas'}</t>
+          <t>Kansas</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_'kentucky',_'value':_'kentucky'}</t>
+          <t>kentucky</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': 'Kentucky', 'value': 'Kentucky'}</t>
+          <t>Kentucky</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_18,_'label':_'louisiana',_'value':_'louisiana'}</t>
+          <t>louisiana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 18, 'label': 'Louisiana', 'value': 'Louisiana'}</t>
+          <t>Louisiana</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_19,_'label':_'maine',_'value':_'maine'}</t>
+          <t>maine</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 19, 'label': 'Maine', 'value': 'Maine'}</t>
+          <t>Maine</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'maryland',_'value':_'maryland'}</t>
+          <t>maryland</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'Maryland', 'value': 'Maryland'}</t>
+          <t>Maryland</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'massachusetts',_'value':_'massachusetts'}</t>
+          <t>massachusetts</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Massachusetts', 'value': 'Massachusetts'}</t>
+          <t>Massachusetts</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'michigan',_'value':_'michigan'}</t>
+          <t>michigan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'Michigan', 'value': 'Michigan'}</t>
+          <t>Michigan</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'minnesota',_'value':_'minnesota'}</t>
+          <t>minnesota</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'Minnesota', 'value': 'Minnesota'}</t>
+          <t>Minnesota</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'mississippi',_'value':_'mississippi'}</t>
+          <t>mississippi</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'Mississippi', 'value': 'Mississippi'}</t>
+          <t>Mississippi</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_25,_'label':_'missouri',_'value':_'missouri'}</t>
+          <t>missouri</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 25, 'label': 'Missouri', 'value': 'Missouri'}</t>
+          <t>Missouri</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_26,_'label':_'montana',_'value':_'montana'}</t>
+          <t>montana</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 26, 'label': 'Montana', 'value': 'Montana'}</t>
+          <t>Montana</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_27,_'label':_'nebraska',_'value':_'nebraska'}</t>
+          <t>nebraska</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 27, 'label': 'Nebraska', 'value': 'Nebraska'}</t>
+          <t>Nebraska</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_28,_'label':_'nevada',_'value':_'nevada'}</t>
+          <t>nevada</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 28, 'label': 'Nevada', 'value': 'Nevada'}</t>
+          <t>Nevada</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_29,_'label':_'new_hampshire',_'value':_'new_hampshire'}</t>
+          <t>new_hampshire</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 29, 'label': 'New Hampshire', 'value': 'New Hampshire'}</t>
+          <t>New Hampshire</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_30,_'label':_'new_jersey',_'value':_'new_jersey'}</t>
+          <t>new_jersey</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 30, 'label': 'New Jersey', 'value': 'New Jersey'}</t>
+          <t>New Jersey</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_31,_'label':_'new_mexico',_'value':_'new_mexico'}</t>
+          <t>new_mexico</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 31, 'label': 'New Mexico', 'value': 'New Mexico'}</t>
+          <t>New Mexico</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_32,_'label':_'new_york',_'value':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 32, 'label': 'New York', 'value': 'New York'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_33,_'label':_'north_carolina',_'value':_'north_carolina'}</t>
+          <t>north_carolina</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 33, 'label': 'North Carolina', 'value': 'North Carolina'}</t>
+          <t>North Carolina</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_34,_'label':_'north_dakota',_'value':_'north_dakota'}</t>
+          <t>north_dakota</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 34, 'label': 'North Dakota', 'value': 'North Dakota'}</t>
+          <t>North Dakota</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_35,_'label':_'ohio',_'value':_'ohio'}</t>
+          <t>ohio</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 35, 'label': 'Ohio', 'value': 'Ohio'}</t>
+          <t>Ohio</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_36,_'label':_'oklahoma',_'value':_'oklahoma'}</t>
+          <t>oklahoma</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 36, 'label': 'Oklahoma', 'value': 'Oklahoma'}</t>
+          <t>Oklahoma</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_37,_'label':_'oregon',_'value':_'oregon'}</t>
+          <t>oregon</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 37, 'label': 'Oregon', 'value': 'Oregon'}</t>
+          <t>Oregon</t>
         </is>
       </c>
     </row>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_38,_'label':_'pennsylvania',_'value':_'pennsylvania'}</t>
+          <t>pennsylvania</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 38, 'label': 'Pennsylvania', 'value': 'Pennsylvania'}</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_39,_'label':_'rhode_island',_'value':_'rhode_island'}</t>
+          <t>rhode_island</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 39, 'label': 'Rhode Island', 'value': 'Rhode Island'}</t>
+          <t>Rhode Island</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1849,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_40,_'label':_'tennessee',_'value':_'tennessee'}</t>
+          <t>tennessee</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 40, 'label': 'Tennessee', 'value': 'Tennessee'}</t>
+          <t>Tennessee</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_41,_'label':_'texas',_'value':_'texas'}</t>
+          <t>texas</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 41, 'label': 'Texas', 'value': 'Texas'}</t>
+          <t>Texas</t>
         </is>
       </c>
     </row>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_42,_'label':_'utah',_'value':_'utah'}</t>
+          <t>utah</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 42, 'label': 'Utah', 'value': 'Utah'}</t>
+          <t>Utah</t>
         </is>
       </c>
     </row>
@@ -1900,12 +1900,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_43,_'label':_'vermont',_'value':_'vermont'}</t>
+          <t>vermont</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 43, 'label': 'Vermont', 'value': 'Vermont'}</t>
+          <t>Vermont</t>
         </is>
       </c>
     </row>
@@ -1917,12 +1917,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_44,_'label':_'virginia',_'value':_'virginia'}</t>
+          <t>virginia</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 44, 'label': 'Virginia', 'value': 'Virginia'}</t>
+          <t>Virginia</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_45,_'label':_'washington',_'value':_'washington'}</t>
+          <t>washington</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 45, 'label': 'Washington', 'value': 'Washington'}</t>
+          <t>Washington</t>
         </is>
       </c>
     </row>
@@ -1951,12 +1951,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_46,_'label':_'west_virginia',_'value':_'west_virginia'}</t>
+          <t>west_virginia</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 46, 'label': 'West Virginia', 'value': 'West Virginia'}</t>
+          <t>West Virginia</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_47,_'label':_'wisconsin',_'value':_'wisconsin'}</t>
+          <t>wisconsin</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 47, 'label': 'Wisconsin', 'value': 'Wisconsin'}</t>
+          <t>Wisconsin</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2002,12 +2002,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'conditional',_'value':_'conditional'}</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Conditional', 'value': 'Conditional'}</t>
+          <t>Conditional</t>
         </is>
       </c>
     </row>
@@ -2036,12 +2036,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'city_manager',_'value':_'city_manager'}</t>
+          <t>city_manager</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'City Manager', 'value': 'City Manager'}</t>
+          <t>City Manager</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mayor',_'value':_'mayor'}</t>
+          <t>mayor</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mayor', 'value': 'Mayor'}</t>
+          <t>Mayor</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'city_councilor',_'value':_'city_councilor'}</t>
+          <t>city_councilor</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'City Councilor', 'value': 'City Councilor'}</t>
+          <t>City Councilor</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'city_council_member',_'value':_'city_council_member'}</t>
+          <t>city_council_member</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'City Council Member', 'value': 'City Council Member'}</t>
+          <t>City Council Member</t>
         </is>
       </c>
     </row>
@@ -2121,12 +2121,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'city_council_member_-_2nd',_'value':_'city_council_member_-_2nd'}</t>
+          <t>city_council_member_-_2nd</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'City Council Member - 2nd', 'value': 'City Council Member - 2nd'}</t>
+          <t>City Council Member - 2nd</t>
         </is>
       </c>
     </row>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'city_councilor_at-large',_'value':_'city_councilor_at-large'}</t>
+          <t>city_councilor_at-large</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'City Councilor At-Large', 'value': 'City Councilor At-Large'}</t>
+          <t>City Councilor At-Large</t>
         </is>
       </c>
     </row>
@@ -2155,12 +2155,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'city_councilor_-_2nd',_'value':_'city_councilor_-_2nd'}</t>
+          <t>city_councilor_-_2nd</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'City Councilor - 2nd', 'value': 'City Councilor - 2nd'}</t>
+          <t>City Councilor - 2nd</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2172,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'mayor_-_elect',_'value':_'mayor_-_elect'}</t>
+          <t>mayor_-_elect</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Mayor - Elect', 'value': 'Mayor - Elect'}</t>
+          <t>Mayor - Elect</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'city_councilor_-_3rd',_'value':_'city_councilor_-_3rd'}</t>
+          <t>city_councilor_-_3rd</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'City Councilor - 3rd', 'value': 'City Councilor - 3rd'}</t>
+          <t>City Councilor - 3rd</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'city_councilor_-_4th',_'value':_'city_councilor_-_4th'}</t>
+          <t>city_councilor_-_4th</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'City Councilor - 4th', 'value': 'City Councilor - 4th'}</t>
+          <t>City Councilor - 4th</t>
         </is>
       </c>
     </row>
@@ -2223,12 +2223,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'city_manager_-_elect',_'value':_'city_manager_-_elect'}</t>
+          <t>city_manager_-_elect</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'City Manager - Elect', 'value': 'City Manager - Elect'}</t>
+          <t>City Manager - Elect</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2240,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'city_manager_-_2nd',_'value':_'city_manager_-_2nd'}</t>
+          <t>city_manager_-_2nd</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'City Manager - 2nd', 'value': 'City Manager - 2nd'}</t>
+          <t>City Manager - 2nd</t>
         </is>
       </c>
     </row>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'city_manager_-_3rd',_'value':_'city_manager_-_3rd'}</t>
+          <t>city_manager_-_3rd</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'City Manager - 3rd', 'value': 'City Manager - 3rd'}</t>
+          <t>City Manager - 3rd</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2274,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'city_manager_-_4th',_'value':_'city_manager_-_4th'}</t>
+          <t>city_manager_-_4th</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'City Manager - 4th', 'value': 'City Manager - 4th'}</t>
+          <t>City Manager - 4th</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'city_manager_-_5th',_'value':_'city_manager_-_5th'}</t>
+          <t>city_manager_-_5th</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'City Manager - 5th', 'value': 'City Manager - 5th'}</t>
+          <t>City Manager - 5th</t>
         </is>
       </c>
     </row>
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'city_councilor_-_1st_assistant',_'value':_'city_councilor_-_1st_assistant'}</t>
+          <t>city_councilor_-_1st_assistant</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 'City Councilor - 1st Assistant', 'value': 'City Councilor - 1st Assistant'}</t>
+          <t>City Councilor - 1st Assistant</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_'city_councilor_-_2nd_assistant',_'value':_'city_councilor_-_2nd_assistant'}</t>
+          <t>city_councilor_-_2nd_assistant</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': 'City Councilor - 2nd Assistant', 'value': 'City Councilor - 2nd Assistant'}</t>
+          <t>City Councilor - 2nd Assistant</t>
         </is>
       </c>
     </row>
@@ -2342,12 +2342,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'id':_18,_'label':_'city_councilor_-_3rd_assistant',_'value':_'city_councilor_-_3rd_assistant'}</t>
+          <t>city_councilor_-_3rd_assistant</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'id': 18, 'label': 'City Councilor - 3rd Assistant', 'value': 'City Councilor - 3rd Assistant'}</t>
+          <t>City Councilor - 3rd Assistant</t>
         </is>
       </c>
     </row>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'id':_19,_'label':_'city_councilor_-_4th_assistant',_'value':_'city_councilor_-_4th_assistant'}</t>
+          <t>city_councilor_-_4th_assistant</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'id': 19, 'label': 'City Councilor - 4th Assistant', 'value': 'City Councilor - 4th Assistant'}</t>
+          <t>City Councilor - 4th Assistant</t>
         </is>
       </c>
     </row>
@@ -2376,12 +2376,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'city_councilor_-_5th_assistant',_'value':_'city_councilor_-_5th_assistant'}</t>
+          <t>city_councilor_-_5th_assistant</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'City Councilor - 5th Assistant', 'value': 'City Councilor - 5th Assistant'}</t>
+          <t>City Councilor - 5th Assistant</t>
         </is>
       </c>
     </row>
@@ -2393,12 +2393,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'city_councilor_-_6th_assistant',_'value':_'city_councilor_-_6th_assistant'}</t>
+          <t>city_councilor_-_6th_assistant</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'City Councilor - 6th Assistant', 'value': 'City Councilor - 6th Assistant'}</t>
+          <t>City Councilor - 6th Assistant</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'city_councilor_-_7th_assistant',_'value':_'city_councilor_-_7th_assistant'}</t>
+          <t>city_councilor_-_7th_assistant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'City Councilor - 7th Assistant', 'value': 'City Councilor - 7th Assistant'}</t>
+          <t>City Councilor - 7th Assistant</t>
         </is>
       </c>
     </row>
@@ -2427,12 +2427,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'city_councilor_-_8th_assistant',_'value':_'city_councilor_-_8th_assistant'}</t>
+          <t>city_councilor_-_8th_assistant</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'City Councilor - 8th Assistant', 'value': 'City Councilor - 8th Assistant'}</t>
+          <t>City Councilor - 8th Assistant</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'city_councilor_-_9th_assistant',_'value':_'city_councilor_-_9th_assistant'}</t>
+          <t>city_councilor_-_9th_assistant</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'City Councilor - 9th Assistant', 'value': 'City Councilor - 9th Assistant'}</t>
+          <t>City Councilor - 9th Assistant</t>
         </is>
       </c>
     </row>
@@ -2461,12 +2461,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'id':_25,_'label':_'city_councilor_-_10th_assistant',_'value':_'city_councilor_-_10th_assistant'}</t>
+          <t>city_councilor_-_10th_assistant</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'id': 25, 'label': 'City Councilor - 10th Assistant', 'value': 'City Councilor - 10th Assistant'}</t>
+          <t>City Councilor - 10th Assistant</t>
         </is>
       </c>
     </row>
@@ -2478,12 +2478,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2495,12 +2495,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2512,12 +2512,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'conditional',_'value':_'conditional'}</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Conditional', 'value': 'Conditional'}</t>
+          <t>Conditional</t>
         </is>
       </c>
     </row>
@@ -2529,12 +2529,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
